--- a/docs/demo/02_vehicles_demo.xlsx
+++ b/docs/demo/02_vehicles_demo.xlsx
@@ -147,10 +147,10 @@
         </is>
       </c>
       <c r="H2" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I2" s="2">
-        <v>1500</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="3">
@@ -190,10 +190,10 @@
         </is>
       </c>
       <c r="H3" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="2">
-        <v>3000</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="4">
@@ -233,10 +233,10 @@
         </is>
       </c>
       <c r="H4" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="I4" s="2">
-        <v>4500</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="5">
@@ -276,10 +276,10 @@
         </is>
       </c>
       <c r="H5" s="2">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="I5" s="2">
-        <v>6000</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="6">
@@ -319,10 +319,10 @@
         </is>
       </c>
       <c r="H6" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="I6" s="2">
-        <v>7500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="7">
@@ -362,10 +362,10 @@
         </is>
       </c>
       <c r="H7" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I7" s="2">
-        <v>9000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="8">
@@ -405,10 +405,10 @@
         </is>
       </c>
       <c r="H8" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I8" s="2">
-        <v>10500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="9">
@@ -448,10 +448,10 @@
         </is>
       </c>
       <c r="H9" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="I9" s="2">
-        <v>12000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="10">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="H10" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="I10" s="2">
-        <v>13500</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="11">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="H11" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="I11" s="2">
-        <v>15000</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="12">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="H12" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I12" s="2">
-        <v>16500</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="13">
@@ -620,10 +620,10 @@
         </is>
       </c>
       <c r="H13" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I13" s="2">
-        <v>18000</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="14">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="H14" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="I14" s="2">
-        <v>19500</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="15">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="H15" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I15" s="2">
-        <v>21000</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="16">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="H16" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I16" s="2">
-        <v>22500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="17">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="H17" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I17" s="2">
-        <v>24000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="18">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="H18" s="2">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="I18" s="2">
-        <v>25500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="19">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="H19" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I19" s="2">
-        <v>27000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="20">
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="H20" s="2">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="I20" s="2">
-        <v>28500</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="21">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="H21" s="2">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="I21" s="2">
-        <v>30000</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="22">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="H22" s="2">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="I22" s="2">
-        <v>31500</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="23">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="H23" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I23" s="2">
-        <v>33000</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="24">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="H24" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="I24" s="2">
-        <v>34500</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="25">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="H25" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I25" s="2">
-        <v>36000</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="26">
@@ -1182,7 +1182,7 @@
         <v>2024</v>
       </c>
       <c r="I26" s="2">
-        <v>37500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="27">
@@ -1222,10 +1222,10 @@
         </is>
       </c>
       <c r="H27" s="2">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="I27" s="2">
-        <v>39000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="28">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="H28" s="2">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="I28" s="2">
-        <v>40500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="29">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="H29" s="2">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="I29" s="2">
-        <v>42000</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="30">
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="H30" s="2">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="I30" s="2">
-        <v>43500</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="31">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="H31" s="2">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="I31" s="2">
-        <v>45000</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="32">
